--- a/main/StructureDefinition-bc-batch-response-bundle.xlsx
+++ b/main/StructureDefinition-bc-batch-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -2247,7 +2247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>191</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>240</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>265</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>272</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>290</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>304</v>
       </c>
@@ -11197,7 +11197,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>311</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>328</v>
       </c>
@@ -14257,12 +14257,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN113">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
